--- a/test/excel/xlsx/roundtrip/formulas.xlsx
+++ b/test/excel/xlsx/roundtrip/formulas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-71511/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-96170/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A24558C0-67C7-A34F-BF10-72BC358D750A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0A0BC9A-2EF2-BE4D-8BE6-5E36C57142A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -442,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -620,6 +620,18 @@
       <c r="C26" cm="1">
         <f t="array" ref="C26">NETWORKDAYS.INTL(DATE(2025,1,1),DATE(2025,1,31),1)</f>
         <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C27" t="str" cm="1">
+        <f t="array" ref="C27">""</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C28" t="str" cm="1">
+        <f t="array" ref="C28">B4&amp;""</f>
+        <v/>
       </c>
     </row>
   </sheetData>
